--- a/backend/static/Salary_2026-02_single.xlsx
+++ b/backend/static/Salary_2026-02_single.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,6 +725,86 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TEST EMPLOYEE 031614</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TEST0001234</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>test@example.com</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/backend/static/Salary_2026-02_single.xlsx
+++ b/backend/static/Salary_2026-02_single.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,17 +526,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SUMITRA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>EKTA SURESHKUMAR RAVAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50100333464010</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KKBK0001417</t>
+          <t>HDFC0000501</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3757.14</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -548,8 +552,16 @@
           <t>SALARY 2026-02</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9987240051</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>mesekta123@gmail.com</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>PB-HSR</t>
@@ -564,16 +576,16 @@
         <v>28</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3857.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3757.14</v>
       </c>
     </row>
     <row r="3">
@@ -594,17 +606,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EKTA SURESHKUMAR RAVAL</t>
+          <t>RAJAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18890100018790</t>
+          <t>50100333464010</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BARB0KAMELA</t>
+          <t>HDFC0000501</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -620,8 +632,16 @@
           <t>SALARY 2026-02</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9987240051</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>mesekta123@gmail.com</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>PB-HSR</t>
@@ -666,17 +686,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TEST EMPLOYEE 025414</t>
+          <t>AMMA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>50100333464010</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TEST0001234</t>
+          <t>HDFC0000501</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -694,12 +714,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9999999999</t>
+          <t>9987240051</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>test@example.com</t>
+          <t>mesekta123@gmail.com</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -746,17 +766,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TEST EMPLOYEE 031614</t>
+          <t>BOBBY CHETRY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>1487000100094392</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TEST0001234</t>
+          <t>PUN80148700</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -774,12 +794,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9999999999</t>
+          <t>9387807268</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>test@example.com</t>
+          <t>rohitchetry5314@gmali.com</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -805,6 +825,966 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ROHIT CHETRY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1487000100094392</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PUN80148700</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9387807268</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>rohitchetry5314@gmail.com</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PREM CHETRI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>35107636627</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SBIN0007384</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9101682046</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>chetriprem93@gmail.com</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OMKAR PRAKASH ABNAVE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>50100580557836</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HDFC0001204</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>9321565465</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>abnaveomkar1302@gmail.com</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>28</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GOPAL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>50100580557836</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HDFC0001204</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9321565465</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>abnaveomkar1302@gmail.com</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>28</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KRISHNA CHETRI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10144408295</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IDFB0080187</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9366709032</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>krishnaxetri45846@gmail.com</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DHERAN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10144408295</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IDFB0080187</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9366709032</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>krishnaxetri45846@gmail.com</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>28</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KIRAN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10144408295</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IDFB0080187</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>9366709032</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>krishnaxetri45846@gmail.com</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JUSHI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>501318210000571</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BKID0005013</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9366709032</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>krishnaxetri45846@gmail.com</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>28</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ANUPRIYA ORAON</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2501255685235035</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AUBL0002556</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9732742184</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>krishnaxetri45846@gmail.com</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BARKHA SABAR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2501255685235045</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AUBL0002556</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8147482214</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>krishnaxetri45846@gmail.com</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>28</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UJWAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>101444082995</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>IDFB0080187</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9036951778</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>krishnaxetri45846@gmail.com</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BABIL GURUNG</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50100333464010</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>HDFC0000501</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8247248360</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>babilgurung88@gmail.com</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PB-HSR</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>28</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/backend/static/Salary_2026-02_single.xlsx
+++ b/backend/static/Salary_2026-02_single.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,21 +526,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EKTA SURESHKUMAR RAVAL</t>
+          <t>SAHIL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50100333464010</t>
+          <t>06040100035505</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HDFC0000501</t>
+          <t>BARB0AMBAZA</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3757.14</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,38 +554,38 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9987240051</t>
+          <t>8390292539</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>mesekta123@gmail.com</t>
+          <t>aniruddhsuryavanshi033@gmail.com</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N2" t="n">
         <v>28</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3857.14</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3757.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -606,17 +606,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RAJAN</t>
+          <t>ANJALI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50100333464010</t>
+          <t>05940100008080</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HDFC0000501</t>
+          <t>BARBOCHITRI</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -634,22 +634,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9987240051</t>
+          <t>8390292539</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>mesekta123@gmail.com</t>
+          <t>aniruddhsuryavanshi033@gmail.com</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -686,17 +686,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AMMA</t>
+          <t>LAXMI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50100333464010</t>
+          <t>06040100035505</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HDFC0000501</t>
+          <t>BARB0AMBAZA</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -714,22 +714,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9987240051</t>
+          <t>8390292539</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>mesekta123@gmail.com</t>
+          <t>aniruddhsuryavanshi033@gmail.com</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BOBBY CHETRY</t>
+          <t>SUMITRA RAWAL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1487000100094392</t>
+          <t>8146512289</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PUN80148700</t>
+          <t>KKBK0001417</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -794,22 +794,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9387807268</t>
+          <t>8390292539</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>rohitchetry5314@gmali.com</t>
+          <t>aniruddhsuryavanshi033@gmail.com</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -846,17 +846,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ROHIT CHETRY</t>
+          <t>BISHA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1487000100094392</t>
+          <t>06040100035505</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PUN80148700</t>
+          <t>BARB0AMBAZA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -874,22 +874,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9387807268</t>
+          <t>8390292539</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>rohitchetry5314@gmail.com</t>
+          <t>aniruddhsuryavanshi033@gmail.com</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -926,17 +926,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PREM CHETRI</t>
+          <t>SAVITRI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35107636627</t>
+          <t>06040100035505</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SBIN0007384</t>
+          <t>BARB0AMBAZA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -954,22 +954,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9101682046</t>
+          <t>8390292539</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>chetriprem93@gmail.com</t>
+          <t>aniruddhsuryavanshi033@gmail.com</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OMKAR PRAKASH ABNAVE</t>
+          <t>ASHIK SHAW</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50100580557836</t>
+          <t>4748230682</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HDFC0001204</t>
+          <t>KKBK0000811</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9321565465</t>
+          <t>9175414141</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>abnaveomkar1302@gmail.com</t>
+          <t>ashikshaw072@gmail.com</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1086,17 +1086,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GOPAL</t>
+          <t>KRISHNA GOWALA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50100580557836</t>
+          <t>41506520714</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HDFC0001204</t>
+          <t>SBIN0002084</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1114,22 +1114,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9321565465</t>
+          <t>9382018857</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>abnaveomkar1302@gmail.com</t>
+          <t>kg2327445@gmail.com</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1166,17 +1166,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KRISHNA CHETRI</t>
+          <t>SUBASHAN  GOWLA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10144408295</t>
+          <t>2501421779290400</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IDFB0080187</t>
+          <t>AUBL0004217</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1194,22 +1194,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9366709032</t>
+          <t>9635550738</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>krishnaxetri45846@gmail.com</t>
+          <t>gopesubash57@gmail.com</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DHERAN</t>
+          <t>GOVIND KUMAR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10144408295</t>
+          <t>1248408962</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IDFB0080187</t>
+          <t>KKBK0001949</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1274,22 +1274,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9366709032</t>
+          <t>8853374172</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>krishnaxetri45846@gmail.com</t>
+          <t>govindkumar95664@gmail.com</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KIRAN</t>
+          <t>SAKSHI SANTOSH GUNDAL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10144408295</t>
+          <t>41122334644</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IDFB0080187</t>
+          <t>SBIN0060203</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1354,22 +1354,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9366709032</t>
+          <t>9373434989</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>krishnaxetri45846@gmail.com</t>
+          <t>sgundal12@gmail.com</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JUSHI</t>
+          <t>NIVESH NAIK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>501318210000571</t>
+          <t>2501422177307903</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BKID0005013</t>
+          <t>AUBL0004221</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1434,22 +1434,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9366709032</t>
+          <t>7224032430</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>krishnaxetri45846@gmail.com</t>
+          <t>niveshnaik88@gmail.com</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1486,17 +1486,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ANUPRIYA ORAON</t>
+          <t>SWAPNIL GUNDAP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2501255685235035</t>
+          <t>33486828345</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AUBL0002556</t>
+          <t>SBINO00517</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1514,22 +1514,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9732742184</t>
+          <t>9960886185</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>krishnaxetri45846@gmail.com</t>
+          <t>niveshnaik88@gmail.com</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BARKHA SABAR</t>
+          <t>SAPANA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2501255685235045</t>
+          <t>0218101080555</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AUBL0002556</t>
+          <t>CNRB0000218</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1594,22 +1594,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8147482214</t>
+          <t>9960886185</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>krishnaxetri45846@gmail.com</t>
+          <t>niveshnaik88@gmail.com</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UJWAL</t>
+          <t>PRAKASH</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>101444082995</t>
+          <t>2501422177307903</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IDFB0080187</t>
+          <t>AUBL0004221</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1674,22 +1674,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9036951778</t>
+          <t>9960886185</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>krishnaxetri45846@gmail.com</t>
+          <t>niveshnaik88@gmail.com</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1726,17 +1726,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BABIL GURUNG</t>
+          <t>SUNITA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>50100333464010</t>
+          <t>06040100035505</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HDFC0000501</t>
+          <t>BARB0AMBAZA</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1754,22 +1754,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8247248360</t>
+          <t>8390292539</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>babilgurung88@gmail.com</t>
+          <t>niveshnaik88@gmail.com</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PB-HSR</t>
+          <t>PB-KAL</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1785,6 +1785,326 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JAYASHREE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>41122334644</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SBIN0060203</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>9373434989</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>sgundal12@gmail.com</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>28</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MAYUR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>203650067122</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FINO0001157</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>9960886185</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>niveshnaik88@gmail.com</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>28</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LAXMI RAWAL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>61219678984</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SBIN0031910</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9960886185</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>gadhwal.veeru@gmail.com</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>28</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PAB_VENDOR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>55205000830</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ANIRUDDH SURYAWANSHI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>06040100035505</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BARB0AMBAZA</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SALARY</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SALARY 2026-02</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>8390292539</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>aniruddhsuryavanshi033@gmail.com</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PB-KAL</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>28</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>0</v>
       </c>
     </row>
